--- a/data/attendance/AMPHI_حموي_علمي_1.xlsx
+++ b/data/attendance/AMPHI_حموي_علمي_1.xlsx
@@ -493,7 +493,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="87">
   <si>
-    <t>حموي علمي 1  |  AMPHI  |  BAC  |  عبد السلام حموي</t>
+    <t>حموي علمي 1  |  AMPHI  |  BAC  |  حموي عبد السلام</t>
   </si>
   <si>
     <t>class_id=2</t>
